--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444666370446814</v>
       </c>
       <c r="C2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>27670146</v>
+        <v>4276926</v>
       </c>
       <c r="L2" t="n">
-        <v>16036710</v>
+        <v>2202033</v>
       </c>
       <c r="M2" t="n">
-        <v>4016174</v>
+        <v>482866</v>
       </c>
       <c r="N2" t="n">
-        <v>217597</v>
+        <v>15470</v>
       </c>
       <c r="O2" t="n">
-        <v>2396332</v>
+        <v>296047</v>
       </c>
       <c r="P2" t="n">
-        <v>943939</v>
+        <v>114616</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999873042106628</v>
+        <v>0.9999867677688599</v>
       </c>
       <c r="R2" t="n">
-        <v>0.902493417263031</v>
+        <v>0.8238059282302856</v>
       </c>
       <c r="S2" t="n">
-        <v>0.805726170539856</v>
+        <v>0.6648156642913818</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7580049633979797</v>
+        <v>0.5763595700263977</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4519223570823669</v>
+        <v>0.1429521888494492</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8024969100952148</v>
+        <v>0.6325317621231079</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8674227595329285</v>
+        <v>0.7561219930648804</v>
       </c>
       <c r="X2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.95653235912323</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911312997341156</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580047488212585</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.66214919090271</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646644592285</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024449655927808</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>27670146</v>
+        <v>4276926</v>
       </c>
       <c r="E3" t="n">
-        <v>2635444</v>
+        <v>749050</v>
       </c>
       <c r="F3" t="n">
-        <v>49889</v>
+        <v>16848</v>
       </c>
       <c r="G3" t="n">
-        <v>5300</v>
+        <v>1626</v>
       </c>
       <c r="H3" t="n">
-        <v>2631</v>
+        <v>1084</v>
       </c>
       <c r="I3" t="n">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="J3" t="n">
-        <v>60417236</v>
+        <v>10069536</v>
       </c>
       <c r="K3" t="n">
-        <v>65142931</v>
+        <v>10455679</v>
       </c>
       <c r="L3" t="n">
-        <v>74934530</v>
+        <v>12010577</v>
       </c>
       <c r="M3" t="n">
-        <v>91607367</v>
+        <v>15125189</v>
       </c>
       <c r="N3" t="n">
-        <v>97696021</v>
+        <v>16233748</v>
       </c>
       <c r="O3" t="n">
-        <v>94849390</v>
+        <v>15734017</v>
       </c>
       <c r="P3" t="n">
-        <v>97191703</v>
+        <v>16185592</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9112948179244995</v>
+        <v>0.8476579785346985</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8142629861831665</v>
+        <v>0.66825270652771</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7163476943969727</v>
+        <v>0.5159425735473633</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4059009552001953</v>
+        <v>0.1728414446115494</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7839227914810181</v>
+        <v>0.5804899930953979</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8137229681015015</v>
+        <v>0.5925144553184509</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1194510</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51498</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>40960</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60417720</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66811145</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77057112</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92093936</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>97778931</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95139602</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97256450</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575998783111572</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099897742271423</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574815392494202</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616687178611755</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015793204307556</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319545241795172</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2825799</v>
+        <v>861610</v>
       </c>
       <c r="E4" t="n">
-        <v>16036710</v>
+        <v>2202033</v>
       </c>
       <c r="F4" t="n">
-        <v>741708</v>
+        <v>198372</v>
       </c>
       <c r="G4" t="n">
-        <v>30762</v>
+        <v>11447</v>
       </c>
       <c r="H4" t="n">
-        <v>55212</v>
+        <v>19981</v>
       </c>
       <c r="I4" t="n">
-        <v>4557</v>
+        <v>1766</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>84</v>
       </c>
       <c r="K4" t="n">
-        <v>2989519</v>
+        <v>914741</v>
       </c>
       <c r="L4" t="n">
-        <v>3866715</v>
+        <v>1110213</v>
       </c>
       <c r="M4" t="n">
-        <v>1282174</v>
+        <v>354920</v>
       </c>
       <c r="N4" t="n">
-        <v>263895</v>
+        <v>92748</v>
       </c>
       <c r="O4" t="n">
-        <v>589763</v>
+        <v>171988</v>
       </c>
       <c r="P4" t="n">
-        <v>144272</v>
+        <v>36968</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999993622303009</v>
+        <v>0.9999933838844299</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9068728089332581</v>
+        <v>0.8355617523193359</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8099720478057861</v>
+        <v>0.6665297150611877</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7365878224372864</v>
+        <v>0.5444802045822144</v>
       </c>
       <c r="U4" t="n">
-        <v>0.427677184343338</v>
+        <v>0.1564823389053345</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7931011319160461</v>
+        <v>0.6053944826126099</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8397152423858643</v>
+        <v>0.6643943786621094</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1233664</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>498690</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33091</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6876</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1321305</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1744133</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>795605</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>180985</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299551</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570658206939697</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910650908946991</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577430844306946</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619088649749756</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017719030380249</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>105795</v>
+        <v>36670</v>
       </c>
       <c r="E5" t="n">
-        <v>1069591</v>
+        <v>304841</v>
       </c>
       <c r="F5" t="n">
-        <v>4016174</v>
+        <v>482866</v>
       </c>
       <c r="G5" t="n">
-        <v>100170</v>
+        <v>29933</v>
       </c>
       <c r="H5" t="n">
-        <v>292448</v>
+        <v>73959</v>
       </c>
       <c r="I5" t="n">
-        <v>22261</v>
+        <v>7606</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2693404</v>
+        <v>768654</v>
       </c>
       <c r="L5" t="n">
-        <v>3658045</v>
+        <v>1093177</v>
       </c>
       <c r="M5" t="n">
-        <v>1590285</v>
+        <v>453025</v>
       </c>
       <c r="N5" t="n">
-        <v>318487</v>
+        <v>74034</v>
       </c>
       <c r="O5" t="n">
-        <v>660515</v>
+        <v>213948</v>
       </c>
       <c r="P5" t="n">
-        <v>216086</v>
+        <v>78824</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999951124191284</v>
+        <v>0.9999948740005493</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9423030018806458</v>
+        <v>0.8974540233612061</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9236034154891968</v>
+        <v>0.8657779097557068</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9708368182182312</v>
+        <v>0.9507830739021301</v>
       </c>
       <c r="U5" t="n">
-        <v>0.994087278842926</v>
+        <v>0.9898402690887451</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9873062968254089</v>
+        <v>0.9764902591705322</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963414072990417</v>
+        <v>0.9929463863372803</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48367</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>512041</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59802</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175016</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1287418</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1772729</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>799024</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181374</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300857</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735144376754761</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642943739891052</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838101863861084</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210821151733</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939042329788208</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983834028244019</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>56170</v>
+        <v>15211</v>
       </c>
       <c r="E6" t="n">
-        <v>82648</v>
+        <v>20867</v>
       </c>
       <c r="F6" t="n">
-        <v>125481</v>
+        <v>26757</v>
       </c>
       <c r="G6" t="n">
-        <v>217597</v>
+        <v>15470</v>
       </c>
       <c r="H6" t="n">
-        <v>49506</v>
+        <v>10067</v>
       </c>
       <c r="I6" t="n">
-        <v>4618</v>
+        <v>1111</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38939</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32230</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65403</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41916</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>1628</v>
+        <v>1215</v>
       </c>
       <c r="E7" t="n">
-        <v>74817</v>
+        <v>33308</v>
       </c>
       <c r="F7" t="n">
-        <v>350774</v>
+        <v>106645</v>
       </c>
       <c r="G7" t="n">
-        <v>120459</v>
+        <v>46319</v>
       </c>
       <c r="H7" t="n">
-        <v>2396332</v>
+        <v>296047</v>
       </c>
       <c r="I7" t="n">
-        <v>112708</v>
+        <v>26446</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4866</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178032</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45539</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>4215</v>
+        <v>2147</v>
       </c>
       <c r="F8" t="n">
-        <v>14322</v>
+        <v>6298</v>
       </c>
       <c r="G8" t="n">
-        <v>7204</v>
+        <v>3423</v>
       </c>
       <c r="H8" t="n">
-        <v>189966</v>
+        <v>66897</v>
       </c>
       <c r="I8" t="n">
-        <v>943939</v>
+        <v>114616</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
